--- a/BaoCao/9.2.TestCaseSprint2.xlsx
+++ b/BaoCao/9.2.TestCaseSprint2.xlsx
@@ -37,13 +37,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="675">
   <si>
-    <t>TEST CASE SYSTEM SPRINT 1</t>
+    <t>TEST CASE SYSTEM SPRINT 2</t>
   </si>
   <si>
     <t>Tên dự án</t>
   </si>
   <si>
-    <t xml:space="preserve">Website bán hàng tích hợp AI tìm kiếm
+    <t xml:space="preserve">SmartTrial
 </t>
   </si>
   <si>
@@ -86,7 +86,7 @@
     <t>Project Name</t>
   </si>
   <si>
-    <t>SMARTTRIAL</t>
+    <t>SmartTrial</t>
   </si>
   <si>
     <t>Module Code</t>
@@ -342,7 +342,7 @@
     <t>Khung giờ mới hiển thị ngay cho học sinh mà không cần tải lại trang</t>
   </si>
   <si>
-    <t>SMARTRIAL</t>
+    <t>SmartTrial</t>
   </si>
   <si>
     <t>GUI Show Đặt lịch học thử</t>
@@ -361,7 +361,7 @@
     <t>Truy cập được trang có nút mở popup</t>
   </si>
   <si>
-    <t>Popup hiển thị giữa màn hình, nền phía sau bị làm mờ; có icon lịch, tiêu đề "Đăng ký Học thử Miễn phí 100%", phụ đề "EduLink kết nối gia sư phù hợp trong 24 giờ" và nút đóng (X) góc phải; đường kẻ ngăn cách phần đầu và nội dung</t>
+    <t>Popup hiển thị giữa màn hình, nền phía sau bị làm mờ; có icon lịch, tiêu đề "Đăng ký Học thử Miễn phí 100%", phụ đề "SmartTrial kết nối gia sư phù hợp trong 24 giờ" và nút đóng (X) góc phải; đường kẻ ngăn cách phần đầu và nội dung</t>
   </si>
   <si>
     <t>Khôi</t>
@@ -454,7 +454,7 @@
 5. Nhấn "Xác nhận giữ chỗ học thử"</t>
   </si>
   <si>
-    <t>Hiển thị thông báo giữ chỗ thành công (EduLink liên hệ trong 24 giờ); popup đóng; yêu cầu học thử được ghi nhận</t>
+    <t>Hiển thị thông báo giữ chỗ thành công (SmartTrial liên hệ trong 24 giờ); popup đóng; yêu cầu học thử được ghi nhận</t>
   </si>
   <si>
     <t>FUNC-DLHT03</t>
@@ -1031,7 +1031,7 @@
     <t>1. Quan sát phần cuối phiếu đăng ký</t>
   </si>
   <si>
-    <t>Hiển thị dòng "Học phí ca 90 phút: 350.000đ", "Phí nền tảng EduLink: Miễn phí 100%" (màu xanh lá), dòng "Tổng thanh toán" in đậm kèm số tiền lớn màu xanh; nút "Xác nhận đặt lịch &amp; Giữ chỗ" (nền xanh, có icon dấu tick) nổi bật, chiếm trọn chiều rộng phiếu</t>
+    <t>Hiển thị dòng "Học phí ca 90 phút: 350.000đ", "Phí nền tảng SmartTrial: Miễn phí 100%" (màu xanh lá), dòng "Tổng thanh toán" in đậm kèm số tiền lớn màu xanh; nút "Xác nhận đặt lịch &amp; Giữ chỗ" (nền xanh, có icon dấu tick) nổi bật, chiếm trọn chiều rộng phiếu</t>
   </si>
   <si>
     <t>FUNC-YCDL-01</t>
@@ -1240,7 +1240,7 @@
     <t>Đang trong phòng học trực tuyến 1:1 (buổi Tư vấn/Học trực tuyến)</t>
   </si>
   <si>
-    <t>Hiển thị logo "EduLink" kèm nhãn "1:1 Class", tên lớp/chuyên đề, nhãn "Face ID: Đã nhận diện học viên &amp; giáo viên (100% minh bạch)", trạng thái ghi hình (REC + thời gian) và thời lượng buổi học, icon cài đặt, icon trợ giúp, nút "Rời phòng" (màu đỏ) và icon tài khoản</t>
+    <t>Hiển thị logo "SmartTrial" kèm nhãn "1:1 Class", tên lớp/chuyên đề, nhãn "Face ID: Đã nhận diện học viên &amp; giáo viên (100% minh bạch)", trạng thái ghi hình (REC + thời gian) và thời lượng buổi học, icon cài đặt, icon trợ giúp, nút "Rời phòng" (màu đỏ) và icon tài khoản</t>
   </si>
   <si>
     <t>GUI-TVTT-02</t>
@@ -1501,7 +1501,7 @@
     <t>Đang ở trang "Tin nhắn / Chatbox"</t>
   </si>
   <si>
-    <t>Hiển thị logo EduLink, các mục: Trang chủ, Lớp học của tôi, Lịch học, Tin nhắn/Chatbox (đang chọn, nổi bật), Tìm gia sư, Đánh giá; icon chuông thông báo (có chấm đỏ) và icon tài khoản</t>
+    <t>Hiển thị logo SmartTrial, các mục: Trang chủ, Lớp học của tôi, Lịch học, Tin nhắn/Chatbox (đang chọn, nổi bật), Tìm gia sư, Đánh giá; icon chuông thông báo (có chấm đỏ) và icon tài khoản</t>
   </si>
   <si>
     <t>GUI-CBAI-02</t>
@@ -1749,7 +1749,7 @@
     <t>Chatbot AI tự động trả lời câu hỏi thường gặp</t>
   </si>
   <si>
-    <t>1. Mở hội thoại với "Trợ giảng EduLink" (hỗ trợ kỹ thuật)
+    <t>1. Mở hội thoại với "Trợ giảng SmartTrial" (hỗ trợ kỹ thuật)
 2. Gửi một câu hỏi thường gặp (VD: "Làm sao để quét lại Face ID?")</t>
   </si>
   <si>
@@ -1765,7 +1765,7 @@
     <t>Chatbot AI chuyển tiếp cho nhân viên hỗ trợ khi không xử lý được</t>
   </si>
   <si>
-    <t>1. Gửi câu hỏi phức tạp hoặc ngoài phạm vi chatbot có thể trả lời cho "Trợ giảng EduLink"
+    <t>1. Gửi câu hỏi phức tạp hoặc ngoài phạm vi chatbot có thể trả lời cho "Trợ giảng SmartTrial"
 2. Yêu cầu gặp nhân viên hỗ trợ thực nếu chatbot không giải quyết được</t>
   </si>
   <si>
@@ -1815,7 +1815,7 @@
     <t>1. Quan sát dòng dưới danh sách khoản thu</t>
   </si>
   <si>
-    <t>Hiển thị "Hạn nộp học phí: 15/04/2025" và nhãn "Miễn phí phí giao dịch cổng trường" kèm dấu tích xanh</t>
+    <t>Hiển thị "Hạn nộp học phí: 15/04/2025" và nhãn "Miễn phí giao dịch nền tảng SmartTrial" kèm dấu tích xanh</t>
   </si>
   <si>
     <t>GUI-TT-04</t>
